--- a/2026/URIARTE 630/Febrero/EXPENSAS-Febrero.xlsx
+++ b/2026/URIARTE 630/Febrero/EXPENSAS-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\URIARTE 630\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\URIARTE 630\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F5CEFF-A05C-4BB6-8036-745B1793242A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B112F4DF-7039-401B-80FE-94420CDDB5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$10</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="69">
   <si>
     <t>UF</t>
   </si>
@@ -224,16 +237,13 @@
     <t>Multas</t>
   </si>
   <si>
-    <t>La multa aplicada corresponde a ruidos molestos y a la colocación de indumentaria colgada en las barandas, fuera de los espacios habilitados para tal fin.</t>
-  </si>
-  <si>
     <t>Vto. 13/03</t>
   </si>
   <si>
     <t>ARTICULOS DE LIMPIEZA</t>
   </si>
   <si>
-    <t>DOARTERO - TRABAJO DE HERRERIA</t>
+    <t>-------</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1118,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1259,7 +1269,7 @@
     <xf numFmtId="16" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1272,10 +1282,54 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1283,13 +1337,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1314,57 +1366,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1729,42 +1738,42 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>27</v>
       </c>
@@ -1775,10 +1784,10 @@
         <v>62</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1786,12 +1795,12 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
@@ -1803,24 +1812,24 @@
       </c>
       <c r="F11" s="112"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="45" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="106"/>
       <c r="C12" s="101">
-        <f>71833+71833*20%</f>
-        <v>86199.6</v>
+        <f>86199+86199*6%</f>
+        <v>91370.94</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="30" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="31">
-        <v>-523530.13955200627</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-943204.07785200619</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="45" t="s">
         <v>33</v>
       </c>
@@ -1834,10 +1843,10 @@
       </c>
       <c r="F13" s="98">
         <f>'prorrateo '!F10</f>
-        <v>260620.1367</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>865324.38150000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="52" t="s">
         <v>46</v>
       </c>
@@ -1851,33 +1860,31 @@
       </c>
       <c r="F14" s="99">
         <f>-C26</f>
-        <v>-598146.46499999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-502236.04499999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="52" t="s">
         <v>51</v>
       </c>
       <c r="B15" s="106"/>
-      <c r="C15" s="148">
+      <c r="C15" s="43">
         <v>162057</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="97"/>
       <c r="F15" s="100"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="52" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="107"/>
-      <c r="C16" s="101">
-        <v>16081.76</v>
-      </c>
+      <c r="C16" s="101"/>
       <c r="E16" s="97"/>
       <c r="F16" s="100"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="52" t="s">
         <v>31</v>
       </c>
@@ -1889,18 +1896,18 @@
       <c r="E17" s="97"/>
       <c r="F17" s="100"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="52" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="108"/>
-      <c r="C18" s="149">
+      <c r="C18" s="101">
         <v>140182.85999999999</v>
       </c>
       <c r="E18" s="97"/>
       <c r="F18" s="100"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="52" t="s">
         <v>57</v>
       </c>
@@ -1911,14 +1918,14 @@
       <c r="E19" s="97"/>
       <c r="F19" s="100"/>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="109"/>
       <c r="C20" s="102">
         <f>SUM(C12:C19)</f>
-        <v>475646.46499999997</v>
+        <v>464736.04499999998</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="32" t="s">
@@ -1926,10 +1933,10 @@
       </c>
       <c r="F20" s="33">
         <f>SUM(F12:F18)</f>
-        <v>-861056.4678520062</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>-580115.74135200609</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="48" t="s">
         <v>15</v>
       </c>
@@ -1939,13 +1946,13 @@
       <c r="E21" s="12"/>
       <c r="F21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="45" t="s">
-        <v>69</v>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="52" t="s">
+        <v>67</v>
       </c>
       <c r="B22" s="106"/>
       <c r="C22" s="43">
-        <v>85000</v>
+        <v>8550</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="114" t="s">
@@ -1953,58 +1960,54 @@
       </c>
       <c r="F22" s="114"/>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B23" s="106"/>
-      <c r="C23" s="148">
+      <c r="C23" s="43">
         <v>28950</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="114"/>
       <c r="F23" s="114"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="52" t="s">
-        <v>68</v>
-      </c>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="52"/>
       <c r="B24" s="106"/>
-      <c r="C24" s="148">
-        <v>8550</v>
-      </c>
+      <c r="C24" s="110"/>
       <c r="D24" s="4"/>
       <c r="E24" s="114"/>
       <c r="F24" s="114"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="44">
         <f>SUM(C21:C24)</f>
-        <v>122500</v>
+        <v>37500</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="114"/>
       <c r="F25" s="114"/>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="26" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="73">
         <f>+C25+C20</f>
-        <v>598146.46499999997</v>
+        <v>502236.04499999998</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="114"/>
       <c r="F26" s="114"/>
     </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="39" t="s">
         <v>18</v>
       </c>
@@ -2013,21 +2016,21 @@
       <c r="E27" s="114"/>
       <c r="F27" s="114"/>
     </row>
-    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="15" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="114"/>
       <c r="F28" s="114"/>
     </row>
-    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="25"/>
       <c r="B29" s="19"/>
       <c r="C29" s="75"/>
       <c r="E29" s="114"/>
       <c r="F29" s="114"/>
     </row>
-    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="29"/>
       <c r="B30" s="28"/>
       <c r="C30" s="76">
@@ -2036,7 +2039,7 @@
       <c r="E30" s="114"/>
       <c r="F30" s="114"/>
     </row>
-    <row r="31" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="34"/>
       <c r="B31" s="35"/>
       <c r="C31" s="76">
@@ -2045,21 +2048,21 @@
       <c r="E31" s="114"/>
       <c r="F31" s="114"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="40"/>
       <c r="B32" s="41"/>
       <c r="C32" s="77"/>
       <c r="E32" s="114"/>
       <c r="F32" s="114"/>
     </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="113"/>
       <c r="B33" s="113"/>
       <c r="C33" s="76"/>
       <c r="E33" s="114"/>
       <c r="F33" s="114"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="29"/>
       <c r="B34" s="28"/>
       <c r="C34" s="76">
@@ -2067,7 +2070,7 @@
       </c>
       <c r="F34" s="5"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="36" t="s">
         <v>17</v>
       </c>
@@ -2077,84 +2080,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C36" s="76"/>
       <c r="F36" s="5"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C37" s="78">
         <f>C36+C26</f>
-        <v>598146.46499999997</v>
+        <v>502236.04499999998</v>
       </c>
       <c r="F37" s="5"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="36" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="37"/>
       <c r="C38" s="50">
         <f>+C26+C35</f>
-        <v>598146.46499999997</v>
+        <v>502236.04499999998</v>
       </c>
       <c r="E38" s="10"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D43" s="5"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D46" s="10"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D47" s="10"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="12"/>
       <c r="B59" s="11"/>
       <c r="C59" s="13"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="11"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -2181,53 +2184,53 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.90625" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.36328125" customWidth="1"/>
+    <col min="4" max="4" width="6.90625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.90625" customWidth="1"/>
+    <col min="8" max="8" width="13.90625" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="14"/>
+    <col min="11" max="12" width="14.36328125" customWidth="1"/>
+    <col min="13" max="13" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A1" s="144" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ENERO</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
       <c r="D1" s="83"/>
       <c r="E1" s="84" t="s">
         <v>26</v>
       </c>
       <c r="F1" s="83"/>
-      <c r="G1" s="125" t="s">
+      <c r="G1" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="127"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="141"/>
       <c r="K1" s="104"/>
-      <c r="L1" s="128">
+      <c r="L1" s="142">
         <f>O1</f>
-        <v>680294.07499999995</v>
-      </c>
-      <c r="M1" s="129"/>
+        <v>502236.04499999998</v>
+      </c>
+      <c r="M1" s="143"/>
       <c r="O1" s="14">
-        <v>680294.07499999995</v>
+        <v>502236.04499999998</v>
       </c>
       <c r="P1" s="14"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="85" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 13/03</v>
@@ -2249,38 +2252,38 @@
         <v>413723.43999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="144" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="125" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="123" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="142" t="s">
+      <c r="E3" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="142" t="s">
+      <c r="F3" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="142" t="s">
+      <c r="G3" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="142" t="s">
+      <c r="H3" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="146" t="s">
+      <c r="I3" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="146" t="s">
+      <c r="J3" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="K3" s="142" t="s">
+      <c r="K3" s="123" t="s">
         <v>65</v>
       </c>
       <c r="L3" s="6" t="s">
@@ -2290,20 +2293,20 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="145"/>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="126"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="143"/>
+      <c r="C4" s="124"/>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="143"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="124"/>
       <c r="L4" s="80" t="str">
         <f>A2</f>
         <v>Vto. 13/03</v>
@@ -2312,7 +2315,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="86">
         <v>1</v>
       </c>
@@ -2326,20 +2329,23 @@
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
-        <v>130310.06835</v>
-      </c>
-      <c r="F5" s="43"/>
+        <v>295483</v>
+      </c>
+      <c r="F5" s="43">
+        <f>E5</f>
+        <v>295483</v>
+      </c>
       <c r="G5" s="81">
         <f>E5-F5</f>
-        <v>130310.06835</v>
+        <v>0</v>
       </c>
       <c r="H5" s="82">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>10946.045741400001</v>
+        <v>0</v>
       </c>
       <c r="I5" s="23">
         <f>L$1*B5</f>
-        <v>142861.75574999998</v>
+        <v>105469.56945</v>
       </c>
       <c r="J5" s="9">
         <f>J$2*D5</f>
@@ -2348,14 +2354,14 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9">
         <f t="shared" ref="L5:L9" si="0">I5+J5+H5+G5+K5</f>
-        <v>284117.86984140001</v>
+        <v>105469.56945</v>
       </c>
       <c r="M5" s="88">
         <f>L5+L5*4%</f>
-        <v>295482.58463505603</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>109688.35222799999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="86">
         <v>2</v>
       </c>
@@ -2369,20 +2375,20 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
-        <v>215130.5227424</v>
+        <v>342048.53865276161</v>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="81">
         <f t="shared" ref="G6:G9" si="1">E6-F6</f>
-        <v>215130.5227424</v>
+        <v>342048.53865276161</v>
       </c>
       <c r="H6" s="82">
         <f t="shared" ref="H6:H9" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>18070.963910361603</v>
+        <v>28732.077246831977</v>
       </c>
       <c r="I6" s="23">
         <f>L$1*B6</f>
-        <v>108847.052</v>
+        <v>80357.767200000002</v>
       </c>
       <c r="J6" s="9">
         <f>J$2*D6</f>
@@ -2391,14 +2397,14 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9">
         <f t="shared" si="0"/>
-        <v>342048.53865276161</v>
+        <v>451138.38309959357</v>
       </c>
       <c r="M6" s="88">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>355730.48019887204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>469183.91842357733</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="86">
         <v>3</v>
       </c>
@@ -2410,38 +2416,37 @@
       </c>
       <c r="D7" s="49"/>
       <c r="E7" s="23">
-        <v>130310.06835</v>
-      </c>
-      <c r="F7" s="43"/>
+        <v>326976.39656640001</v>
+      </c>
+      <c r="F7" s="43">
+        <v>284117.87</v>
+      </c>
       <c r="G7" s="81">
         <f t="shared" si="1"/>
-        <v>130310.06835</v>
+        <v>42858.526566400018</v>
       </c>
       <c r="H7" s="82">
         <f t="shared" si="2"/>
-        <v>10946.045741400001</v>
+        <v>3600.1162315776019</v>
       </c>
       <c r="I7" s="23">
         <f>L$1*B7</f>
-        <v>142861.75574999998</v>
+        <v>105469.56945</v>
       </c>
       <c r="J7" s="9">
         <v>0</v>
       </c>
-      <c r="K7" s="110">
-        <f>I7*0.3</f>
-        <v>42858.526724999996</v>
-      </c>
+      <c r="K7" s="147"/>
       <c r="L7" s="9">
         <f>I7+J7+H7+G7+K7</f>
-        <v>326976.39656640001</v>
+        <v>151928.21224797762</v>
       </c>
       <c r="M7" s="88">
         <f t="shared" si="3"/>
-        <v>340055.45242905599</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>158005.34073789671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="86">
         <v>4</v>
       </c>
@@ -2453,11 +2458,11 @@
       </c>
       <c r="D8" s="49"/>
       <c r="E8" s="23">
-        <v>130310.06835</v>
+        <v>142861.75574999998</v>
       </c>
       <c r="F8" s="43">
         <f>E8</f>
-        <v>130310.06835</v>
+        <v>142861.75574999998</v>
       </c>
       <c r="G8" s="81">
         <f t="shared" si="1"/>
@@ -2469,7 +2474,7 @@
       </c>
       <c r="I8" s="23">
         <f>L$1*B8</f>
-        <v>142861.75574999998</v>
+        <v>105469.56945</v>
       </c>
       <c r="J8" s="9">
         <v>0</v>
@@ -2477,14 +2482,14 @@
       <c r="K8" s="9"/>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>142861.75574999998</v>
+        <v>105469.56945</v>
       </c>
       <c r="M8" s="88">
         <f t="shared" si="3"/>
-        <v>148576.22597999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>109688.35222799999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="86">
         <v>5</v>
       </c>
@@ -2496,11 +2501,11 @@
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="23">
-        <v>130310.06835</v>
+        <v>142861.75574999998</v>
       </c>
       <c r="F9" s="43">
         <f>E9</f>
-        <v>130310.06835</v>
+        <v>142861.75574999998</v>
       </c>
       <c r="G9" s="81">
         <f t="shared" si="1"/>
@@ -2512,7 +2517,7 @@
       </c>
       <c r="I9" s="23">
         <f>L$1*B9</f>
-        <v>142861.75574999998</v>
+        <v>105469.56945</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2520,14 +2525,14 @@
       <c r="K9" s="9"/>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>142861.75574999998</v>
+        <v>105469.56945</v>
       </c>
       <c r="M9" s="88">
         <f t="shared" si="3"/>
-        <v>148576.22597999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>109688.35222799999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="89" t="s">
         <v>7</v>
       </c>
@@ -2542,23 +2547,23 @@
       </c>
       <c r="E10" s="93">
         <f>SUM(E5:E9)</f>
-        <v>736370.79614240001</v>
+        <v>1250231.4467191617</v>
       </c>
       <c r="F10" s="93">
         <f>SUM(F5:F9)</f>
-        <v>260620.1367</v>
+        <v>865324.38150000002</v>
       </c>
       <c r="G10" s="93">
         <f t="shared" si="4"/>
-        <v>345440.59109240002</v>
+        <v>342048.53865276161</v>
       </c>
       <c r="H10" s="93">
         <f t="shared" si="4"/>
-        <v>29017.009651761604</v>
+        <v>28732.077246831977</v>
       </c>
       <c r="I10" s="94">
         <f>SUM(I5:I9)</f>
-        <v>680294.07499999995</v>
+        <v>502236.04500000004</v>
       </c>
       <c r="J10" s="94">
         <f t="shared" si="4"/>
@@ -2567,55 +2572,55 @@
       <c r="K10" s="94"/>
       <c r="L10" s="93">
         <f>SUM(L5:L9)</f>
-        <v>1238866.3165605618</v>
+        <v>919475.30369757104</v>
       </c>
       <c r="M10" s="95">
         <f>SUM(M5:M9)</f>
-        <v>1288420.9692229843</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="132"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="132"/>
-      <c r="K11" s="132"/>
-      <c r="L11" s="132"/>
-      <c r="M11" s="132"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>956254.3158454739</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="146"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+    </row>
+    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="117" t="s">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C14" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="134"/>
       <c r="I14" s="54"/>
       <c r="J14" s="55"/>
       <c r="K14" s="59"/>
       <c r="L14" s="59"/>
     </row>
-    <row r="15" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="119" t="s">
+    <row r="15" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C15" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
       <c r="I15" s="56"/>
       <c r="J15" s="57"/>
       <c r="K15" s="59"/>
@@ -2627,7 +2632,7 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C16" s="54"/>
       <c r="D16" s="58"/>
       <c r="E16" s="58"/>
@@ -2647,7 +2652,7 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C17" s="56" t="s">
         <v>38</v>
       </c>
@@ -2669,7 +2674,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C18" s="60"/>
       <c r="D18" s="61"/>
       <c r="E18" s="61"/>
@@ -2687,21 +2692,21 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="115" t="s">
+    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C19" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+      <c r="H19" s="137"/>
       <c r="I19" s="56"/>
       <c r="J19" s="57"/>
       <c r="K19" s="59"/>
       <c r="L19" s="59"/>
     </row>
-    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C20" s="56"/>
       <c r="D20" s="59"/>
       <c r="E20" s="59"/>
@@ -2719,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C21" s="56" t="s">
         <v>40</v>
       </c>
@@ -2733,14 +2738,14 @@
         <v>41</v>
       </c>
       <c r="H21" s="62"/>
-      <c r="I21" s="120" t="s">
+      <c r="I21" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="121"/>
+      <c r="J21" s="132"/>
       <c r="K21" s="71"/>
       <c r="L21" s="71"/>
     </row>
-    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C22" s="56" t="s">
         <v>43</v>
       </c>
@@ -2759,19 +2764,19 @@
       <c r="K22" s="59"/>
       <c r="L22" s="59"/>
     </row>
-    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C23" s="56"/>
       <c r="D23" s="59"/>
       <c r="E23" s="59"/>
       <c r="F23" s="59"/>
       <c r="G23" s="59"/>
       <c r="H23" s="59"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="121"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="132"/>
       <c r="K23" s="71"/>
       <c r="L23" s="71"/>
     </row>
-    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C24" s="69" t="s">
         <v>46</v>
       </c>
@@ -2781,14 +2786,14 @@
       <c r="G24" s="59"/>
       <c r="H24" s="68">
         <f>L$1/5</f>
-        <v>136058.815</v>
+        <v>100447.209</v>
       </c>
       <c r="I24" s="56"/>
       <c r="J24" s="57"/>
       <c r="K24" s="59"/>
       <c r="L24" s="59"/>
     </row>
-    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C25" s="70" t="s">
         <v>30</v>
       </c>
@@ -2805,7 +2810,7 @@
       <c r="K25" s="59"/>
       <c r="L25" s="59"/>
     </row>
-    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C26" s="70" t="s">
         <v>28</v>
       </c>
@@ -2822,7 +2827,7 @@
       <c r="K26" s="59"/>
       <c r="L26" s="59"/>
     </row>
-    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C27" s="70" t="s">
         <v>31</v>
       </c>
@@ -2839,7 +2844,7 @@
       <c r="K27" s="59"/>
       <c r="L27" s="59"/>
     </row>
-    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C28" s="70" t="s">
         <v>29</v>
       </c>
@@ -2856,7 +2861,7 @@
       <c r="K28" s="59"/>
       <c r="L28" s="59"/>
     </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="D29" s="59"/>
       <c r="E29" s="59"/>
       <c r="F29" s="59"/>
@@ -2867,7 +2872,7 @@
       <c r="K29" s="59"/>
       <c r="L29" s="59"/>
     </row>
-    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C30" s="70" t="s">
         <v>34</v>
       </c>
@@ -2884,7 +2889,7 @@
       <c r="K30" s="59"/>
       <c r="L30" s="59"/>
     </row>
-    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="C31" s="56"/>
       <c r="D31" s="59"/>
       <c r="E31" s="59"/>
@@ -2896,55 +2901,55 @@
       <c r="K31" s="59"/>
       <c r="L31" s="59"/>
     </row>
-    <row r="32" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="123" t="s">
+    <row r="32" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C32" s="129" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="124"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="124"/>
+      <c r="D32" s="130"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="130"/>
       <c r="H32" s="105">
         <f>SUM(H24:H31)</f>
-        <v>181425.19750000001</v>
+        <v>145813.59150000001</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="67"/>
       <c r="K32" s="59"/>
       <c r="L32" s="59"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="117" t="s">
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118"/>
+      <c r="D36" s="134"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="134"/>
+      <c r="G36" s="134"/>
+      <c r="H36" s="134"/>
       <c r="I36" s="54"/>
       <c r="J36" s="55"/>
       <c r="K36" s="59"/>
       <c r="L36" s="59"/>
     </row>
-    <row r="37" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="119" t="s">
+    <row r="37" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C37" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118"/>
-      <c r="H37" s="118"/>
+      <c r="D37" s="134"/>
+      <c r="E37" s="134"/>
+      <c r="F37" s="134"/>
+      <c r="G37" s="134"/>
+      <c r="H37" s="134"/>
       <c r="I37" s="56"/>
       <c r="J37" s="57"/>
       <c r="K37" s="59"/>
       <c r="L37" s="59"/>
     </row>
-    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C38" s="54"/>
       <c r="D38" s="58"/>
       <c r="E38" s="58"/>
@@ -2958,7 +2963,7 @@
       <c r="K38" s="59"/>
       <c r="L38" s="59"/>
     </row>
-    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C39" s="56" t="s">
         <v>38</v>
       </c>
@@ -2975,7 +2980,7 @@
       <c r="K39" s="59"/>
       <c r="L39" s="59"/>
     </row>
-    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C40" s="60"/>
       <c r="D40" s="61"/>
       <c r="E40" s="61"/>
@@ -2987,21 +2992,21 @@
       <c r="K40" s="59"/>
       <c r="L40" s="59"/>
     </row>
-    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="115" t="s">
+    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="116"/>
-      <c r="E41" s="116"/>
-      <c r="F41" s="116"/>
-      <c r="G41" s="116"/>
-      <c r="H41" s="116"/>
+      <c r="D41" s="137"/>
+      <c r="E41" s="137"/>
+      <c r="F41" s="137"/>
+      <c r="G41" s="137"/>
+      <c r="H41" s="137"/>
       <c r="I41" s="56"/>
       <c r="J41" s="57"/>
       <c r="K41" s="59"/>
       <c r="L41" s="59"/>
     </row>
-    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C42" s="56"/>
       <c r="D42" s="59"/>
       <c r="E42" s="59"/>
@@ -3013,7 +3018,7 @@
       <c r="K42" s="59"/>
       <c r="L42" s="59"/>
     </row>
-    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C43" s="56" t="s">
         <v>40</v>
       </c>
@@ -3027,14 +3032,14 @@
         <v>41</v>
       </c>
       <c r="H43" s="62"/>
-      <c r="I43" s="120" t="s">
+      <c r="I43" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="J43" s="121"/>
+      <c r="J43" s="132"/>
       <c r="K43" s="71"/>
       <c r="L43" s="71"/>
     </row>
-    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C44" s="56" t="s">
         <v>43</v>
       </c>
@@ -3053,19 +3058,19 @@
       <c r="K44" s="59"/>
       <c r="L44" s="59"/>
     </row>
-    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C45" s="56"/>
       <c r="D45" s="59"/>
       <c r="E45" s="59"/>
       <c r="F45" s="59"/>
       <c r="G45" s="59"/>
       <c r="H45" s="59"/>
-      <c r="I45" s="122"/>
-      <c r="J45" s="121"/>
+      <c r="I45" s="138"/>
+      <c r="J45" s="132"/>
       <c r="K45" s="71"/>
       <c r="L45" s="71"/>
     </row>
-    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C46" s="56" t="s">
         <v>46</v>
       </c>
@@ -3075,14 +3080,14 @@
       <c r="G46" s="59"/>
       <c r="H46" s="68">
         <f>L$1/5</f>
-        <v>136058.815</v>
+        <v>100447.209</v>
       </c>
       <c r="I46" s="56"/>
       <c r="J46" s="57"/>
       <c r="K46" s="59"/>
       <c r="L46" s="59"/>
     </row>
-    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C47" s="56"/>
       <c r="D47" s="59"/>
       <c r="E47" s="59"/>
@@ -3094,7 +3099,7 @@
       <c r="K47" s="59"/>
       <c r="L47" s="59"/>
     </row>
-    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C48" s="56"/>
       <c r="D48" s="59"/>
       <c r="E48" s="59"/>
@@ -3106,54 +3111,54 @@
       <c r="K48" s="59"/>
       <c r="L48" s="59"/>
     </row>
-    <row r="49" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="123" t="s">
+    <row r="49" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C49" s="129" t="s">
         <v>45</v>
       </c>
-      <c r="D49" s="124"/>
-      <c r="E49" s="124"/>
-      <c r="F49" s="124"/>
-      <c r="G49" s="124"/>
+      <c r="D49" s="130"/>
+      <c r="E49" s="130"/>
+      <c r="F49" s="130"/>
+      <c r="G49" s="130"/>
       <c r="H49" s="105">
         <f>M6</f>
-        <v>355730.48019887204</v>
+        <v>469183.91842357733</v>
       </c>
       <c r="I49" s="66"/>
       <c r="J49" s="67"/>
       <c r="K49" s="59"/>
       <c r="L49" s="59"/>
     </row>
-    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="117" t="s">
+    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C52" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="118"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="118"/>
-      <c r="G52" s="118"/>
-      <c r="H52" s="118"/>
+      <c r="D52" s="134"/>
+      <c r="E52" s="134"/>
+      <c r="F52" s="134"/>
+      <c r="G52" s="134"/>
+      <c r="H52" s="134"/>
       <c r="I52" s="54"/>
       <c r="J52" s="55"/>
       <c r="K52" s="59"/>
       <c r="L52" s="59"/>
     </row>
-    <row r="53" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="119" t="s">
+    <row r="53" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C53" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="118"/>
+      <c r="D53" s="134"/>
+      <c r="E53" s="134"/>
+      <c r="F53" s="134"/>
+      <c r="G53" s="134"/>
+      <c r="H53" s="134"/>
       <c r="I53" s="56"/>
       <c r="J53" s="57"/>
       <c r="K53" s="59"/>
       <c r="L53" s="59"/>
     </row>
-    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C54" s="54"/>
       <c r="D54" s="58"/>
       <c r="E54" s="58"/>
@@ -3167,7 +3172,7 @@
       <c r="K54" s="59"/>
       <c r="L54" s="59"/>
     </row>
-    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C55" s="56" t="s">
         <v>38</v>
       </c>
@@ -3184,7 +3189,7 @@
       <c r="K55" s="59"/>
       <c r="L55" s="59"/>
     </row>
-    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C56" s="60"/>
       <c r="D56" s="61"/>
       <c r="E56" s="61"/>
@@ -3196,21 +3201,21 @@
       <c r="K56" s="59"/>
       <c r="L56" s="59"/>
     </row>
-    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="115" t="s">
+    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C57" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="D57" s="116"/>
-      <c r="E57" s="116"/>
-      <c r="F57" s="116"/>
-      <c r="G57" s="116"/>
-      <c r="H57" s="116"/>
+      <c r="D57" s="137"/>
+      <c r="E57" s="137"/>
+      <c r="F57" s="137"/>
+      <c r="G57" s="137"/>
+      <c r="H57" s="137"/>
       <c r="I57" s="56"/>
       <c r="J57" s="57"/>
       <c r="K57" s="59"/>
       <c r="L57" s="59"/>
     </row>
-    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C58" s="56"/>
       <c r="D58" s="59"/>
       <c r="E58" s="59"/>
@@ -3222,7 +3227,7 @@
       <c r="K58" s="59"/>
       <c r="L58" s="59"/>
     </row>
-    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C59" s="56" t="s">
         <v>40</v>
       </c>
@@ -3236,14 +3241,14 @@
         <v>41</v>
       </c>
       <c r="H59" s="62"/>
-      <c r="I59" s="120" t="s">
+      <c r="I59" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="J59" s="121"/>
+      <c r="J59" s="132"/>
       <c r="K59" s="71"/>
       <c r="L59" s="71"/>
     </row>
-    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C60" s="56" t="s">
         <v>43</v>
       </c>
@@ -3262,19 +3267,19 @@
       <c r="K60" s="59"/>
       <c r="L60" s="59"/>
     </row>
-    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C61" s="56"/>
       <c r="D61" s="59"/>
       <c r="E61" s="59"/>
       <c r="F61" s="59"/>
       <c r="G61" s="59"/>
       <c r="H61" s="59"/>
-      <c r="I61" s="122"/>
-      <c r="J61" s="121"/>
+      <c r="I61" s="138"/>
+      <c r="J61" s="132"/>
       <c r="K61" s="71"/>
       <c r="L61" s="71"/>
     </row>
-    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C62" s="56" t="s">
         <v>46</v>
       </c>
@@ -3284,14 +3289,14 @@
       <c r="G62" s="59"/>
       <c r="H62" s="68">
         <f>L$1/5</f>
-        <v>136058.815</v>
+        <v>100447.209</v>
       </c>
       <c r="I62" s="56"/>
       <c r="J62" s="57"/>
       <c r="K62" s="59"/>
       <c r="L62" s="59"/>
     </row>
-    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C63" s="70" t="s">
         <v>30</v>
       </c>
@@ -3308,7 +3313,7 @@
       <c r="K63" s="59"/>
       <c r="L63" s="59"/>
     </row>
-    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C64" s="70" t="s">
         <v>28</v>
       </c>
@@ -3325,7 +3330,7 @@
       <c r="K64" s="59"/>
       <c r="L64" s="59"/>
     </row>
-    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C65" s="70" t="s">
         <v>31</v>
       </c>
@@ -3342,7 +3347,7 @@
       <c r="K65" s="59"/>
       <c r="L65" s="59"/>
     </row>
-    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C66" s="70" t="s">
         <v>29</v>
       </c>
@@ -3359,7 +3364,7 @@
       <c r="K66" s="59"/>
       <c r="L66" s="59"/>
     </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="D67" s="59"/>
       <c r="E67" s="59"/>
       <c r="F67" s="59"/>
@@ -3370,7 +3375,7 @@
       <c r="K67" s="59"/>
       <c r="L67" s="59"/>
     </row>
-    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C68" s="70" t="s">
         <v>34</v>
       </c>
@@ -3387,7 +3392,7 @@
       <c r="K68" s="59"/>
       <c r="L68" s="59"/>
     </row>
-    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C69" s="56"/>
       <c r="D69" s="59"/>
       <c r="E69" s="59"/>
@@ -3399,7 +3404,7 @@
       <c r="K69" s="59"/>
       <c r="L69" s="59"/>
     </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C70" s="56"/>
       <c r="D70" s="59"/>
       <c r="E70" s="59"/>
@@ -3411,7 +3416,7 @@
       <c r="K70" s="59"/>
       <c r="L70" s="59"/>
     </row>
-    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C71" s="56"/>
       <c r="D71" s="59"/>
       <c r="E71" s="59"/>
@@ -3423,55 +3428,55 @@
       <c r="K71" s="59"/>
       <c r="L71" s="59"/>
     </row>
-    <row r="72" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="123" t="s">
+    <row r="72" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C72" s="129" t="s">
         <v>45</v>
       </c>
-      <c r="D72" s="124"/>
-      <c r="E72" s="124"/>
-      <c r="F72" s="124"/>
-      <c r="G72" s="124"/>
+      <c r="D72" s="130"/>
+      <c r="E72" s="130"/>
+      <c r="F72" s="130"/>
+      <c r="G72" s="130"/>
       <c r="H72" s="105">
         <f>SUM(H62:H71)</f>
-        <v>181425.19750000001</v>
+        <v>145813.59150000001</v>
       </c>
       <c r="I72" s="66"/>
       <c r="J72" s="67"/>
       <c r="K72" s="59"/>
       <c r="L72" s="59"/>
     </row>
-    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="117" t="s">
+    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C76" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="D76" s="118"/>
-      <c r="E76" s="118"/>
-      <c r="F76" s="118"/>
-      <c r="G76" s="118"/>
-      <c r="H76" s="118"/>
+      <c r="D76" s="134"/>
+      <c r="E76" s="134"/>
+      <c r="F76" s="134"/>
+      <c r="G76" s="134"/>
+      <c r="H76" s="134"/>
       <c r="I76" s="54"/>
       <c r="J76" s="55"/>
       <c r="K76" s="59"/>
       <c r="L76" s="59"/>
     </row>
-    <row r="77" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="119" t="s">
+    <row r="77" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C77" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="118"/>
-      <c r="E77" s="118"/>
-      <c r="F77" s="118"/>
-      <c r="G77" s="118"/>
-      <c r="H77" s="118"/>
+      <c r="D77" s="134"/>
+      <c r="E77" s="134"/>
+      <c r="F77" s="134"/>
+      <c r="G77" s="134"/>
+      <c r="H77" s="134"/>
       <c r="I77" s="56"/>
       <c r="J77" s="57"/>
       <c r="K77" s="59"/>
       <c r="L77" s="59"/>
     </row>
-    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C78" s="54"/>
       <c r="D78" s="58"/>
       <c r="E78" s="58"/>
@@ -3485,7 +3490,7 @@
       <c r="K78" s="59"/>
       <c r="L78" s="59"/>
     </row>
-    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C79" s="56" t="s">
         <v>38</v>
       </c>
@@ -3502,7 +3507,7 @@
       <c r="K79" s="59"/>
       <c r="L79" s="59"/>
     </row>
-    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C80" s="60"/>
       <c r="D80" s="61"/>
       <c r="E80" s="61"/>
@@ -3514,21 +3519,21 @@
       <c r="K80" s="59"/>
       <c r="L80" s="59"/>
     </row>
-    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="115" t="s">
+    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C81" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="D81" s="116"/>
-      <c r="E81" s="116"/>
-      <c r="F81" s="116"/>
-      <c r="G81" s="116"/>
-      <c r="H81" s="116"/>
+      <c r="D81" s="137"/>
+      <c r="E81" s="137"/>
+      <c r="F81" s="137"/>
+      <c r="G81" s="137"/>
+      <c r="H81" s="137"/>
       <c r="I81" s="56"/>
       <c r="J81" s="57"/>
       <c r="K81" s="59"/>
       <c r="L81" s="59"/>
     </row>
-    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C82" s="56"/>
       <c r="D82" s="59"/>
       <c r="E82" s="59"/>
@@ -3540,7 +3545,7 @@
       <c r="K82" s="59"/>
       <c r="L82" s="59"/>
     </row>
-    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C83" s="56" t="s">
         <v>40</v>
       </c>
@@ -3554,14 +3559,14 @@
         <v>41</v>
       </c>
       <c r="H83" s="62"/>
-      <c r="I83" s="120" t="s">
+      <c r="I83" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="J83" s="121"/>
+      <c r="J83" s="132"/>
       <c r="K83" s="71"/>
       <c r="L83" s="71"/>
     </row>
-    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C84" s="56" t="s">
         <v>43</v>
       </c>
@@ -3580,19 +3585,19 @@
       <c r="K84" s="59"/>
       <c r="L84" s="59"/>
     </row>
-    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C85" s="56"/>
       <c r="D85" s="59"/>
       <c r="E85" s="59"/>
       <c r="F85" s="59"/>
       <c r="G85" s="59"/>
       <c r="H85" s="59"/>
-      <c r="I85" s="122"/>
-      <c r="J85" s="121"/>
+      <c r="I85" s="138"/>
+      <c r="J85" s="132"/>
       <c r="K85" s="71"/>
       <c r="L85" s="71"/>
     </row>
-    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C86" s="56" t="s">
         <v>46</v>
       </c>
@@ -3602,14 +3607,14 @@
       <c r="G86" s="59"/>
       <c r="H86" s="68">
         <f>L$1/5</f>
-        <v>136058.815</v>
+        <v>100447.209</v>
       </c>
       <c r="I86" s="56"/>
       <c r="J86" s="57"/>
       <c r="K86" s="59"/>
       <c r="L86" s="59"/>
     </row>
-    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C87" s="70" t="s">
         <v>30</v>
       </c>
@@ -3626,7 +3631,7 @@
       <c r="K87" s="59"/>
       <c r="L87" s="59"/>
     </row>
-    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C88" s="70" t="s">
         <v>28</v>
       </c>
@@ -3643,7 +3648,7 @@
       <c r="K88" s="59"/>
       <c r="L88" s="59"/>
     </row>
-    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C89" s="70" t="s">
         <v>31</v>
       </c>
@@ -3660,7 +3665,7 @@
       <c r="K89" s="59"/>
       <c r="L89" s="59"/>
     </row>
-    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C90" s="70" t="s">
         <v>29</v>
       </c>
@@ -3677,7 +3682,7 @@
       <c r="K90" s="59"/>
       <c r="L90" s="59"/>
     </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="D91" s="59"/>
       <c r="E91" s="59"/>
       <c r="F91" s="59"/>
@@ -3688,7 +3693,7 @@
       <c r="K91" s="59"/>
       <c r="L91" s="59"/>
     </row>
-    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C92" s="70" t="s">
         <v>34</v>
       </c>
@@ -3705,7 +3710,7 @@
       <c r="K92" s="59"/>
       <c r="L92" s="59"/>
     </row>
-    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="D93" s="59"/>
       <c r="E93" s="59"/>
       <c r="F93" s="59"/>
@@ -3716,55 +3721,55 @@
       <c r="K93" s="59"/>
       <c r="L93" s="59"/>
     </row>
-    <row r="94" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="123" t="s">
+    <row r="94" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C94" s="129" t="s">
         <v>45</v>
       </c>
-      <c r="D94" s="124"/>
-      <c r="E94" s="124"/>
-      <c r="F94" s="124"/>
-      <c r="G94" s="124"/>
+      <c r="D94" s="130"/>
+      <c r="E94" s="130"/>
+      <c r="F94" s="130"/>
+      <c r="G94" s="130"/>
       <c r="H94" s="105">
         <f>SUM(H86:H93)</f>
-        <v>181425.19750000001</v>
+        <v>145813.59150000001</v>
       </c>
       <c r="I94" s="66"/>
       <c r="J94" s="67"/>
       <c r="K94" s="59"/>
       <c r="L94" s="59"/>
     </row>
-    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="117" t="s">
+    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="98" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C98" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="D98" s="118"/>
-      <c r="E98" s="118"/>
-      <c r="F98" s="118"/>
-      <c r="G98" s="118"/>
-      <c r="H98" s="118"/>
+      <c r="D98" s="134"/>
+      <c r="E98" s="134"/>
+      <c r="F98" s="134"/>
+      <c r="G98" s="134"/>
+      <c r="H98" s="134"/>
       <c r="I98" s="54"/>
       <c r="J98" s="55"/>
       <c r="K98" s="59"/>
       <c r="L98" s="59"/>
     </row>
-    <row r="99" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="119" t="s">
+    <row r="99" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C99" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="118"/>
-      <c r="E99" s="118"/>
-      <c r="F99" s="118"/>
-      <c r="G99" s="118"/>
-      <c r="H99" s="118"/>
+      <c r="D99" s="134"/>
+      <c r="E99" s="134"/>
+      <c r="F99" s="134"/>
+      <c r="G99" s="134"/>
+      <c r="H99" s="134"/>
       <c r="I99" s="56"/>
       <c r="J99" s="57"/>
       <c r="K99" s="59"/>
       <c r="L99" s="59"/>
     </row>
-    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C100" s="54"/>
       <c r="D100" s="58"/>
       <c r="E100" s="58"/>
@@ -3778,7 +3783,7 @@
       <c r="K100" s="59"/>
       <c r="L100" s="59"/>
     </row>
-    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C101" s="56" t="s">
         <v>38</v>
       </c>
@@ -3795,7 +3800,7 @@
       <c r="K101" s="59"/>
       <c r="L101" s="59"/>
     </row>
-    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C102" s="60"/>
       <c r="D102" s="61"/>
       <c r="E102" s="61"/>
@@ -3807,21 +3812,21 @@
       <c r="K102" s="59"/>
       <c r="L102" s="59"/>
     </row>
-    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="115" t="s">
+    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C103" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="D103" s="116"/>
-      <c r="E103" s="116"/>
-      <c r="F103" s="116"/>
-      <c r="G103" s="116"/>
-      <c r="H103" s="116"/>
+      <c r="D103" s="137"/>
+      <c r="E103" s="137"/>
+      <c r="F103" s="137"/>
+      <c r="G103" s="137"/>
+      <c r="H103" s="137"/>
       <c r="I103" s="56"/>
       <c r="J103" s="57"/>
       <c r="K103" s="59"/>
       <c r="L103" s="59"/>
     </row>
-    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C104" s="56"/>
       <c r="D104" s="59"/>
       <c r="E104" s="59"/>
@@ -3833,7 +3838,7 @@
       <c r="K104" s="59"/>
       <c r="L104" s="59"/>
     </row>
-    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C105" s="56" t="s">
         <v>40</v>
       </c>
@@ -3847,14 +3852,14 @@
         <v>41</v>
       </c>
       <c r="H105" s="62"/>
-      <c r="I105" s="120" t="s">
+      <c r="I105" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="J105" s="121"/>
+      <c r="J105" s="132"/>
       <c r="K105" s="71"/>
       <c r="L105" s="71"/>
     </row>
-    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C106" s="56" t="s">
         <v>43</v>
       </c>
@@ -3872,19 +3877,19 @@
       <c r="K106" s="59"/>
       <c r="L106" s="59"/>
     </row>
-    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C107" s="56"/>
       <c r="D107" s="59"/>
       <c r="E107" s="59"/>
       <c r="F107" s="59"/>
       <c r="G107" s="59"/>
       <c r="H107" s="59"/>
-      <c r="I107" s="122"/>
-      <c r="J107" s="121"/>
+      <c r="I107" s="138"/>
+      <c r="J107" s="132"/>
       <c r="K107" s="71"/>
       <c r="L107" s="71"/>
     </row>
-    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C108" s="56" t="s">
         <v>46</v>
       </c>
@@ -3894,14 +3899,14 @@
       <c r="G108" s="59"/>
       <c r="H108" s="68">
         <f>L$1/5</f>
-        <v>136058.815</v>
+        <v>100447.209</v>
       </c>
       <c r="I108" s="56"/>
       <c r="J108" s="57"/>
       <c r="K108" s="59"/>
       <c r="L108" s="59"/>
     </row>
-    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C109" s="70" t="s">
         <v>30</v>
       </c>
@@ -3918,7 +3923,7 @@
       <c r="K109" s="59"/>
       <c r="L109" s="59"/>
     </row>
-    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C110" s="70" t="s">
         <v>28</v>
       </c>
@@ -3935,7 +3940,7 @@
       <c r="K110" s="59"/>
       <c r="L110" s="59"/>
     </row>
-    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C111" s="70" t="s">
         <v>31</v>
       </c>
@@ -3952,7 +3957,7 @@
       <c r="K111" s="59"/>
       <c r="L111" s="59"/>
     </row>
-    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="C112" s="70" t="s">
         <v>29</v>
       </c>
@@ -3969,7 +3974,7 @@
       <c r="K112" s="59"/>
       <c r="L112" s="59"/>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="D113" s="59"/>
       <c r="E113" s="59"/>
       <c r="F113" s="59"/>
@@ -3980,7 +3985,7 @@
       <c r="K113" s="59"/>
       <c r="L113" s="59"/>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="C114" s="70" t="s">
         <v>34</v>
       </c>
@@ -3997,7 +4002,7 @@
       <c r="K114" s="59"/>
       <c r="L114" s="59"/>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="D115" s="59"/>
       <c r="E115" s="59"/>
       <c r="F115" s="59"/>
@@ -4008,74 +4013,102 @@
       <c r="K115" s="59"/>
       <c r="L115" s="59"/>
     </row>
-    <row r="116" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="123" t="s">
+    <row r="116" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C116" s="129" t="s">
         <v>45</v>
       </c>
-      <c r="D116" s="124"/>
-      <c r="E116" s="124"/>
-      <c r="F116" s="124"/>
-      <c r="G116" s="124"/>
+      <c r="D116" s="130"/>
+      <c r="E116" s="130"/>
+      <c r="F116" s="130"/>
+      <c r="G116" s="130"/>
       <c r="H116" s="105">
         <f>SUM(H108:H115)</f>
-        <v>181425.19750000001</v>
+        <v>145813.59150000001</v>
       </c>
       <c r="I116" s="66"/>
       <c r="J116" s="67"/>
       <c r="K116" s="59"/>
       <c r="L116" s="59"/>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="133" t="s">
-        <v>66</v>
-      </c>
-      <c r="B119" s="134"/>
-      <c r="C119" s="134"/>
-      <c r="D119" s="134"/>
-      <c r="E119" s="134"/>
-      <c r="F119" s="134"/>
-      <c r="G119" s="134"/>
-      <c r="H119" s="134"/>
-      <c r="I119" s="134"/>
-      <c r="J119" s="134"/>
-      <c r="K119" s="134"/>
-      <c r="L119" s="134"/>
-      <c r="M119" s="135"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="136"/>
-      <c r="B120" s="137"/>
-      <c r="C120" s="137"/>
-      <c r="D120" s="137"/>
-      <c r="E120" s="137"/>
-      <c r="F120" s="137"/>
-      <c r="G120" s="137"/>
-      <c r="H120" s="137"/>
-      <c r="I120" s="137"/>
-      <c r="J120" s="137"/>
-      <c r="K120" s="137"/>
-      <c r="L120" s="137"/>
-      <c r="M120" s="138"/>
-    </row>
-    <row r="121" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="139"/>
-      <c r="B121" s="140"/>
-      <c r="C121" s="140"/>
-      <c r="D121" s="140"/>
-      <c r="E121" s="140"/>
-      <c r="F121" s="140"/>
-      <c r="G121" s="140"/>
-      <c r="H121" s="140"/>
-      <c r="I121" s="140"/>
-      <c r="J121" s="140"/>
-      <c r="K121" s="140"/>
-      <c r="L121" s="140"/>
-      <c r="M121" s="141"/>
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A119" s="148" t="s">
+        <v>68</v>
+      </c>
+      <c r="B119" s="115"/>
+      <c r="C119" s="115"/>
+      <c r="D119" s="115"/>
+      <c r="E119" s="115"/>
+      <c r="F119" s="115"/>
+      <c r="G119" s="115"/>
+      <c r="H119" s="115"/>
+      <c r="I119" s="115"/>
+      <c r="J119" s="115"/>
+      <c r="K119" s="115"/>
+      <c r="L119" s="115"/>
+      <c r="M119" s="116"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A120" s="117"/>
+      <c r="B120" s="118"/>
+      <c r="C120" s="118"/>
+      <c r="D120" s="118"/>
+      <c r="E120" s="118"/>
+      <c r="F120" s="118"/>
+      <c r="G120" s="118"/>
+      <c r="H120" s="118"/>
+      <c r="I120" s="118"/>
+      <c r="J120" s="118"/>
+      <c r="K120" s="118"/>
+      <c r="L120" s="118"/>
+      <c r="M120" s="119"/>
+    </row>
+    <row r="121" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="120"/>
+      <c r="B121" s="121"/>
+      <c r="C121" s="121"/>
+      <c r="D121" s="121"/>
+      <c r="E121" s="121"/>
+      <c r="F121" s="121"/>
+      <c r="G121" s="121"/>
+      <c r="H121" s="121"/>
+      <c r="I121" s="121"/>
+      <c r="J121" s="121"/>
+      <c r="K121" s="121"/>
+      <c r="L121" s="121"/>
+      <c r="M121" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="C116:G116"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I45:J45"/>
     <mergeCell ref="A119:M121"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C4"/>
@@ -4092,34 +4125,6 @@
     <mergeCell ref="C53:H53"/>
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="I107:J107"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="C116:G116"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C99:H99"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C103:H103"/>
-    <mergeCell ref="C76:H76"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="C94:G94"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
